--- a/Listing/HNM03S.xlsx
+++ b/Listing/HNM03S.xlsx
@@ -1,17 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{3CCB2060-8ACD-C545-8B57-B2FCD6A52AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="407">
   <si>
     <t/>
   </si>
@@ -112,6 +129,12 @@
     <t>3</t>
   </si>
   <si>
+    <t>20140873</t>
+  </si>
+  <si>
+    <t>IDM JAS HJ.DISP STLN</t>
+  </si>
+  <si>
     <t>20071123</t>
   </si>
   <si>
@@ -256,16 +279,10 @@
     <t>IDM PLS.SMPH H/B20'S</t>
   </si>
   <si>
-    <t>20125750</t>
-  </si>
-  <si>
-    <t>S/B SKT LNTI ID-51 M</t>
-  </si>
-  <si>
-    <t>20045188</t>
-  </si>
-  <si>
-    <t>IDM SPONS BUSA 2'S</t>
+    <t>20140686</t>
+  </si>
+  <si>
+    <t>SB SPONS &amp; STNLS</t>
   </si>
   <si>
     <t>20044863</t>
@@ -559,10 +576,10 @@
     <t>WHISKAS CF MAC&amp;SAL80</t>
   </si>
   <si>
-    <t>20031236</t>
-  </si>
-  <si>
-    <t>WHSKAS JR OCEAN 450G</t>
+    <t>20141219</t>
+  </si>
+  <si>
+    <t>WHSKAS JR TUNA 180G</t>
   </si>
   <si>
     <t>20064471</t>
@@ -571,10 +588,10 @@
     <t>WHISKAS TUNA 480G</t>
   </si>
   <si>
-    <t>20121358</t>
-  </si>
-  <si>
-    <t>WHISKAS S&amp;C 450G</t>
+    <t>20141220</t>
+  </si>
+  <si>
+    <t>WHSKAS ADLT TUNA 200</t>
   </si>
   <si>
     <t>20088717</t>
@@ -685,9 +702,6 @@
     <t>ME-O CRM CHKN&amp;LVR 60</t>
   </si>
   <si>
-    <t>,(E-3B)</t>
-  </si>
-  <si>
     <t>20102393</t>
   </si>
   <si>
@@ -793,12 +807,6 @@
     <t>IDM SEDOTAN KRTS 20S</t>
   </si>
   <si>
-    <t>20096571</t>
-  </si>
-  <si>
-    <t>IDM BALON WRNA 6'S</t>
-  </si>
-  <si>
     <t>20111707</t>
   </si>
   <si>
@@ -877,12 +885,6 @@
     <t>IDM TALI RAFIA</t>
   </si>
   <si>
-    <t>20045346</t>
-  </si>
-  <si>
-    <t>IDM PISAU+SARUNG PCS</t>
-  </si>
-  <si>
     <t>20126285</t>
   </si>
   <si>
@@ -1042,12 +1044,6 @@
     <t>16</t>
   </si>
   <si>
-    <t>10023747</t>
-  </si>
-  <si>
-    <t>G/SEWU SAPU IJUK PCS</t>
-  </si>
-  <si>
     <t>20076488</t>
   </si>
   <si>
@@ -1120,170 +1116,152 @@
     <t>KEN/M KRAN PLSTK PTH</t>
   </si>
   <si>
+    <t>10016469</t>
+  </si>
+  <si>
+    <t>KEN/M GAS LIGHTER</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>10016469</t>
-  </si>
-  <si>
-    <t>KEN/M GAS LIGHTER</t>
-  </si>
-  <si>
     <t>20053613</t>
   </si>
   <si>
     <t>IDM TALI TAMBANG 6MM</t>
   </si>
   <si>
+    <t>20074350</t>
+  </si>
+  <si>
+    <t>IDM PAYUNG LPT TIGA</t>
+  </si>
+  <si>
     <t>17</t>
   </si>
   <si>
-    <t>20074350</t>
-  </si>
-  <si>
-    <t>IDM PAYUNG LPT TIGA</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20101096</t>
-  </si>
-  <si>
-    <t>IDM SANDAL EVA RUB42</t>
+    <t>20072325</t>
+  </si>
+  <si>
+    <t>IDM SNDAL WNTA 37-38</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>20072325</t>
-  </si>
-  <si>
-    <t>IDM SNDAL WNTA 37-38</t>
+    <t>20037222</t>
+  </si>
+  <si>
+    <t>KEN/M RKT NYM+SNTR B</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>20037222</t>
-  </si>
-  <si>
-    <t>KEN/M RKT NYM+SNTR B</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20101097</t>
-  </si>
-  <si>
-    <t>IDM SANDAL EVA RUB39</t>
+    <t>20093211</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT40</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>20093211</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT40</t>
+    <t>20072320</t>
+  </si>
+  <si>
+    <t>IDM SNDAL PRIA 39-40</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>20072320</t>
-  </si>
-  <si>
-    <t>IDM SNDAL PRIA 39-40</t>
+    <t>20072322</t>
+  </si>
+  <si>
+    <t>IDM SNDAL PRIA 41-42</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>20072322</t>
-  </si>
-  <si>
-    <t>IDM SNDAL PRIA 41-42</t>
+    <t>20093212</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT42</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>20093212</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT42</t>
+    <t>20118405</t>
+  </si>
+  <si>
+    <t>CLARIS EMBER 12 TTP</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>20118405</t>
-  </si>
-  <si>
-    <t>CLARIS EMBER 12 TTP</t>
+    <t>20126380</t>
+  </si>
+  <si>
+    <t>30CLIP WINDPROF BSKT</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>20126380</t>
-  </si>
-  <si>
-    <t>30CLIP WINDPROF BSKT</t>
+    <t>20127779</t>
+  </si>
+  <si>
+    <t>COOGER WALL SOAP W+G</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>20127779</t>
-  </si>
-  <si>
-    <t>COOGER WALL SOAP W+G</t>
+    <t>20126372</t>
+  </si>
+  <si>
+    <t>DISC MULTI TOOHBRUSH</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>20126372</t>
-  </si>
-  <si>
-    <t>DISC MULTI TOOHBRUSH</t>
+    <t>20126381</t>
+  </si>
+  <si>
+    <t>RLR TYPE PWRFUL MOP</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>20126381</t>
-  </si>
-  <si>
-    <t>RLR TYPE PWRFUL MOP</t>
+    <t>20139712</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT38</t>
   </si>
   <si>
     <t>31</t>
   </si>
   <si>
-    <t>20139712</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT38</t>
-  </si>
-  <si>
-    <t>32</t>
+    <t>HNM03S_2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1304,16 +1282,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1662,18 +1640,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F189"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F185"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="1" max="1" width="9.953125" customWidth="1"/>
+    <col min="2" max="2" width="22.05859375" customWidth="1"/>
+    <col min="3" max="3" width="7.93359375" customWidth="1"/>
+    <col min="4" max="5" width="4.03515625" customWidth="1"/>
+    <col min="6" max="6" width="11.02734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1693,7 +1671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1713,7 +1691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1733,7 +1711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1753,7 +1731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1773,7 +1751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1793,7 +1771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1813,7 +1791,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1833,7 +1811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1853,7 +1831,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -1873,7 +1851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1893,7 +1871,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
@@ -1913,7 +1891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -1927,13 +1905,13 @@
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -1947,13 +1925,13 @@
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1967,33 +1945,33 @@
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>42</v>
       </c>
@@ -2007,13 +1985,13 @@
         <v>32</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
@@ -2027,13 +2005,13 @@
         <v>32</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>46</v>
       </c>
@@ -2047,13 +2025,13 @@
         <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>48</v>
       </c>
@@ -2067,13 +2045,13 @@
         <v>32</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>50</v>
       </c>
@@ -2087,13 +2065,13 @@
         <v>32</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>52</v>
       </c>
@@ -2107,13 +2085,13 @@
         <v>32</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
@@ -2127,13 +2105,13 @@
         <v>32</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>56</v>
       </c>
@@ -2147,18 +2125,18 @@
         <v>32</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -2167,13 +2145,13 @@
         <v>32</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>61</v>
       </c>
@@ -2187,18 +2165,18 @@
         <v>32</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -2207,33 +2185,33 @@
         <v>32</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>69</v>
       </c>
@@ -2247,13 +2225,13 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>71</v>
       </c>
@@ -2267,13 +2245,13 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>73</v>
       </c>
@@ -2287,13 +2265,13 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>75</v>
       </c>
@@ -2307,13 +2285,13 @@
         <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>77</v>
       </c>
@@ -2327,13 +2305,13 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>79</v>
       </c>
@@ -2347,13 +2325,13 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>81</v>
       </c>
@@ -2367,13 +2345,13 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>83</v>
       </c>
@@ -2384,16 +2362,16 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>85</v>
       </c>
@@ -2413,7 +2391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>87</v>
       </c>
@@ -2433,7 +2411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>89</v>
       </c>
@@ -2453,7 +2431,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>91</v>
       </c>
@@ -2473,7 +2451,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>93</v>
       </c>
@@ -2493,7 +2471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>95</v>
       </c>
@@ -2513,7 +2491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>97</v>
       </c>
@@ -2527,13 +2505,13 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>99</v>
       </c>
@@ -2553,7 +2531,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>102</v>
       </c>
@@ -2573,7 +2551,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>104</v>
       </c>
@@ -2593,7 +2571,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>107</v>
       </c>
@@ -2613,7 +2591,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>109</v>
       </c>
@@ -2633,7 +2611,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>111</v>
       </c>
@@ -2653,7 +2631,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>113</v>
       </c>
@@ -2673,7 +2651,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>115</v>
       </c>
@@ -2693,7 +2671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>117</v>
       </c>
@@ -2713,7 +2691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>119</v>
       </c>
@@ -2733,7 +2711,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>121</v>
       </c>
@@ -2753,7 +2731,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>123</v>
       </c>
@@ -2773,7 +2751,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>126</v>
       </c>
@@ -2793,7 +2771,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>128</v>
       </c>
@@ -2807,13 +2785,13 @@
         <v>22</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>130</v>
       </c>
@@ -2827,13 +2805,13 @@
         <v>22</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>132</v>
       </c>
@@ -2847,13 +2825,13 @@
         <v>22</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>135</v>
       </c>
@@ -2867,13 +2845,13 @@
         <v>22</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>137</v>
       </c>
@@ -2887,13 +2865,13 @@
         <v>22</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>139</v>
       </c>
@@ -2907,13 +2885,13 @@
         <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>141</v>
       </c>
@@ -2933,7 +2911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>143</v>
       </c>
@@ -2953,7 +2931,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>145</v>
       </c>
@@ -2973,7 +2951,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>147</v>
       </c>
@@ -2993,7 +2971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>149</v>
       </c>
@@ -3013,7 +2991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>151</v>
       </c>
@@ -3033,7 +3011,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>153</v>
       </c>
@@ -3053,7 +3031,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>155</v>
       </c>
@@ -3073,7 +3051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>157</v>
       </c>
@@ -3087,13 +3065,13 @@
         <v>25</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>159</v>
       </c>
@@ -3107,13 +3085,13 @@
         <v>25</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>161</v>
       </c>
@@ -3127,13 +3105,13 @@
         <v>25</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>163</v>
       </c>
@@ -3147,13 +3125,13 @@
         <v>25</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>165</v>
       </c>
@@ -3173,7 +3151,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>168</v>
       </c>
@@ -3184,7 +3162,7 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>4</v>
@@ -3193,7 +3171,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>170</v>
       </c>
@@ -3204,7 +3182,7 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>10</v>
@@ -3213,7 +3191,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>172</v>
       </c>
@@ -3224,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>32</v>
@@ -3233,7 +3211,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>174</v>
       </c>
@@ -3244,7 +3222,7 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>15</v>
@@ -3253,78 +3231,78 @@
         <v>106</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>176</v>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>20134229</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>22</v>
+        <v>406</v>
+      </c>
+      <c r="D80" s="1">
+        <v>8</v>
+      </c>
+      <c r="E80" s="1">
+        <v>5</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>4</v>
@@ -3333,138 +3311,138 @@
         <v>106</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E86" s="1" t="s">
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E88" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F89" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>4</v>
@@ -3473,18 +3451,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>4</v>
@@ -3493,38 +3471,38 @@
         <v>106</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>10</v>
@@ -3533,38 +3511,38 @@
         <v>106</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>32</v>
@@ -3573,38 +3551,38 @@
         <v>106</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>15</v>
@@ -3613,18 +3591,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>15</v>
@@ -3633,38 +3611,38 @@
         <v>106</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>18</v>
@@ -3673,412 +3651,412 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F101" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E102" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F104" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F108" s="1" t="s">
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
+      <c r="B120" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
+      <c r="B121" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4090,15 +4068,15 @@
         <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4113,12 +4091,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4130,15 +4108,15 @@
         <v>10</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4150,15 +4128,15 @@
         <v>10</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4170,15 +4148,15 @@
         <v>32</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4193,12 +4171,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4213,12 +4191,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4233,12 +4211,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4253,12 +4231,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4273,12 +4251,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4293,12 +4271,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4307,18 +4285,18 @@
         <v>167</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4327,1134 +4305,1054 @@
         <v>167</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B135" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E134" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E135" s="1" t="s">
+      <c r="F155" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F135" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E137" s="1" t="s">
+      <c r="F158" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F137" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E138" s="1" t="s">
+      <c r="F159" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F138" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E139" s="1" t="s">
+      <c r="F160" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F139" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E140" s="1" t="s">
+      <c r="F161" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F140" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E141" s="1" t="s">
+      <c r="F162" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F141" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B143" s="1" t="s">
+      <c r="F163" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E170" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B157" s="1" t="s">
+      <c r="F170" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B170" s="1" t="s">
+      <c r="E171" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="1" t="s">
+      <c r="F171" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="B172" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="B173" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E172" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="F172" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" s="1" t="s">
+      <c r="F173" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="B174" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="F174" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E174" s="1" t="s">
+      <c r="B175" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="F174" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="F175" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E175" s="1" t="s">
+      <c r="B176" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="F175" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="F176" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E176" s="1" t="s">
+      <c r="B177" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F176" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" s="1" t="s">
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="F177" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E177" s="1" t="s">
+      <c r="B178" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="F177" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="F178" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E178" s="1" t="s">
+      <c r="B179" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="F178" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E179" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="F179" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E179" s="1" t="s">
+      <c r="B180" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F179" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="F180" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E180" s="1" t="s">
+      <c r="B181" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="F180" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="F181" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E181" s="1" t="s">
+      <c r="B182" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="F181" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="F182" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E182" s="1" t="s">
+      <c r="B183" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F182" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="F183" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E183" s="1" t="s">
+      <c r="B184" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="F183" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="F184" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E184" s="1" t="s">
+      <c r="B185" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F184" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="F185" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="F189" s="1" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>